--- a/outputs/All_States_negative_prices.xlsx
+++ b/outputs/All_States_negative_prices.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3367,6 +3367,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3378,7 +3412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6301,6 +6335,40 @@
         <v>0.07000000000000001</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6312,7 +6380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9235,6 +9303,40 @@
         <v>0.35</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9246,7 +9348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12169,6 +12271,40 @@
         <v>1.46</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12180,7 +12316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15103,6 +15239,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/All_States_negative_prices.xlsx
+++ b/outputs/All_States_negative_prices.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3401,6 +3401,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3412,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6369,6 +6403,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6380,7 +6448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9337,6 +9405,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9348,7 +9450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12305,6 +12407,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12316,7 +12452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15273,6 +15409,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/All_States_negative_prices.xlsx
+++ b/outputs/All_States_negative_prices.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3435,6 +3435,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3446,7 +3480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6437,6 +6471,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6448,7 +6516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9439,6 +9507,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9450,7 +9552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12441,6 +12543,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12452,7 +12588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15443,6 +15579,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/All_States_negative_prices.xlsx
+++ b/outputs/All_States_negative_prices.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3469,6 +3469,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3480,7 +3514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6505,6 +6539,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6516,7 +6584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9541,6 +9609,40 @@
         <v>0.27</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9552,7 +9654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12577,6 +12679,40 @@
         <v>0.44</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12588,7 +12724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15613,6 +15749,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/All_States_negative_prices.xlsx
+++ b/outputs/All_States_negative_prices.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NSW" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="QLD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="VIC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TAS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSW" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QLD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1</v>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.52</v>
+        <v>0.31</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.17</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.1</v>
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.1</v>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0</v>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2.47</v>
+        <v>1.6</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>1.25</v>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.13</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.52</v>
+        <v>0.03</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>0.03</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>4.72</v>
+        <v>4.13</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>2.6</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>0.17</v>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>0.03</v>
@@ -1402,31 +1402,31 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
@@ -1436,19 +1436,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>13.61</v>
+        <v>13.58</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.77</v>
+        <v>8.74</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>1.21</v>
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>27.12</v>
+        <v>26.6</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>18.75</v>
+        <v>18.68</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>14.27</v>
+        <v>14.2</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>10.56</v>
+        <v>10.52</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>2.57</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>24.26</v>
+        <v>24.06</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>19.89</v>
+        <v>19.86</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>18.08</v>
@@ -1538,16 +1538,16 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>8.19</v>
+        <v>7.85</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>6.91</v>
+        <v>6.88</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>0.97</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>4.47</v>
+        <v>4.37</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>2.45</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.24</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3.42</v>
+        <v>3.27</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1.97</v>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0.14</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0.59</v>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0.9399999999999999</v>
@@ -1844,13 +1844,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>5.71</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>5.28</v>
+        <v>5.24</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>4.7</v>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>18.78</v>
+        <v>18.61</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>16.18</v>
+        <v>16.11</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>14.83</v>
@@ -1896,10 +1896,10 @@
         <v>5.8</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>0</v>
@@ -1912,25 +1912,25 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>11.83</v>
+        <v>11.73</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>10.32</v>
+        <v>10.25</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>8.4</v>
+        <v>8.33</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>6.79</v>
+        <v>6.72</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>5.14</v>
+        <v>5.07</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>1.01</v>
@@ -1946,25 +1946,25 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>20.59</v>
+        <v>20.38</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>15.07</v>
+        <v>14.93</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>13.51</v>
+        <v>13.4</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>11.63</v>
+        <v>11.56</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>9.17</v>
+        <v>9.1</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>0.38</v>
@@ -1980,22 +1980,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>32.83</v>
+        <v>32.49</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>22.11</v>
+        <v>21.81</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>19.46</v>
+        <v>19.15</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>16.53</v>
+        <v>16.33</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>12.63</v>
+        <v>12.47</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>8.43</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>1.88</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>7.83</v>
+        <v>7.69</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>6.08</v>
+        <v>5.95</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>5.65</v>
+        <v>5.51</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>5.11</v>
+        <v>5.04</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.17</v>
@@ -2051,19 +2051,19 @@
         <v>10.68</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>7.51</v>
+        <v>7.59</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>7.22</v>
+        <v>7.29</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>6.96</v>
+        <v>7.03</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>6.32</v>
+        <v>6.36</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.67</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.22</v>
+        <v>5.95</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>4.47</v>
@@ -2094,7 +2094,7 @@
         <v>3.09</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>13.58</v>
+        <v>13.51</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>11.74</v>
@@ -2128,10 +2128,10 @@
         <v>9.859999999999999</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>7.36</v>
+        <v>7.29</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>2.19</v>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>1.34</v>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>4.72</v>
+        <v>4.44</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>3.58</v>
@@ -2196,7 +2196,7 @@
         <v>2.71</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0.03</v>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>15.99</v>
+        <v>15.09</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>12.6</v>
@@ -2230,7 +2230,7 @@
         <v>9.85</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>2.65</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>17.61</v>
+        <v>17.41</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>14.01</v>
@@ -2264,7 +2264,7 @@
         <v>8.9</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>6.42</v>
+        <v>6.18</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>1.85</v>
@@ -2286,22 +2286,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>39.27</v>
+        <v>39.03</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>35.62</v>
+        <v>35.42</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>32.81</v>
+        <v>32.64</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>25.62</v>
+        <v>25.52</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>24.24</v>
+        <v>24.13</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>16.88</v>
+        <v>16.84</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>3.3</v>
@@ -2320,22 +2320,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>49.13</v>
+        <v>48.76</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>45.83</v>
+        <v>45.6</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>42.81</v>
+        <v>42.54</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>34.71</v>
+        <v>34.48</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>31.59</v>
+        <v>31.38</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>15.93</v>
+        <v>15.66</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>1.61</v>
@@ -2354,19 +2354,19 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>17.4</v>
+        <v>17.26</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>14.65</v>
+        <v>14.51</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>12.99</v>
+        <v>12.88</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>8.4</v>
+        <v>8.33</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>1.35</v>
@@ -2388,19 +2388,19 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>21.24</v>
+        <v>21.2</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>19.76</v>
+        <v>19.72</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>15.83</v>
+        <v>15.76</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>12.16</v>
+        <v>12.1</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>6.82</v>
+        <v>6.85</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0.47</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>2.89</v>
@@ -2437,16 +2437,16 @@
         <v>1.04</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H58" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I58" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="I58" s="3" t="n">
+      <c r="J58" s="3" t="n">
         <v>0.37</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>0.34</v>
       </c>
     </row>
     <row r="59">
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>6.97</v>
+        <v>6.9</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>5.46</v>
+        <v>5.42</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>0.72</v>
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>13.78</v>
+        <v>13.61</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>11.29</v>
+        <v>11.16</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>4.23</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>16.98</v>
+        <v>16.81</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>13.09</v>
+        <v>12.92</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>8.02</v>
+        <v>7.99</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>5.42</v>
+        <v>5.35</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>3.99</v>
@@ -2629,7 +2629,7 @@
         <v>9.74</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>8.33</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>5.58</v>
@@ -2660,19 +2660,19 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>30.71</v>
+        <v>30.54</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>27.45</v>
+        <v>27.28</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>24.9</v>
+        <v>24.76</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>22.01</v>
+        <v>21.98</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>18.58</v>
+        <v>18.55</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>6.42</v>
@@ -2694,16 +2694,16 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>56.7</v>
+        <v>56.67</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>50.97</v>
+        <v>50.94</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>48.54</v>
+        <v>48.51</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>44.06</v>
+        <v>44.03</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>36.6</v>
@@ -2728,19 +2728,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>36.86</v>
+        <v>36.83</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>35.79</v>
+        <v>35.72</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>34.71</v>
+        <v>34.64</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>30.78</v>
+        <v>30.68</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>21.98</v>
+        <v>21.91</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>4.77</v>
@@ -2762,16 +2762,16 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>20.49</v>
+        <v>20.38</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>19.06</v>
+        <v>19.03</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>16.94</v>
+        <v>16.91</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>13.09</v>
+        <v>13.06</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>2.19</v>
@@ -2796,19 +2796,19 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>36.29</v>
+        <v>36.12</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>34.44</v>
+        <v>34.27</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>31.18</v>
+        <v>31.01</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>23.66</v>
+        <v>23.49</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>3.49</v>
+        <v>3.46</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0.1</v>
@@ -2830,16 +2830,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>35.32</v>
+        <v>35.22</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>34.17</v>
+        <v>34.11</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>29.87</v>
+        <v>29.84</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>19.42</v>
+        <v>19.35</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>1.34</v>
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>33.56</v>
+        <v>33.15</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>32.07</v>
+        <v>31.85</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>29.72</v>
+        <v>29.58</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>17.97</v>
+        <v>17.82</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>2.38</v>
@@ -2898,16 +2898,16 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>23.66</v>
+        <v>23.15</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>19.79</v>
+        <v>19.56</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>15.93</v>
+        <v>15.73</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>0.1</v>
@@ -2932,16 +2932,16 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>30.52</v>
+        <v>30.03</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>26.6</v>
+        <v>26.39</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>21.84</v>
+        <v>21.7</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="F73" s="3" t="n">
         <v>0</v>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>19.96</v>
+        <v>19.56</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>17.91</v>
+        <v>17.84</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>11.66</v>
+        <v>11.63</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>0.03</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>7.99</v>
+        <v>7.85</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>6.46</v>
+        <v>6.42</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>2.33</v>
@@ -3034,13 +3034,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>15.66</v>
+        <v>15.52</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>11.76</v>
+        <v>11.69</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>0</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>26.88</v>
+        <v>26.75</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>19.29</v>
+        <v>19.32</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>1.58</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>70.62</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>60.73</v>
+        <v>60.56</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>15.49</v>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>59.85</v>
+        <v>59.48</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>48.62</v>
+        <v>48.45</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>17.27</v>
@@ -3170,31 +3170,31 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>74.72</v>
+        <v>74.41</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>53.85</v>
+        <v>53.33</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>15.97</v>
+        <v>16.04</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="81">
@@ -3204,13 +3204,13 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>49.97</v>
+        <v>48.89</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>23.12</v>
+        <v>22.88</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>7.02</v>
+        <v>6.99</v>
       </c>
       <c r="E81" s="3" t="n">
         <v>4.33</v>
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>18.04</v>
+        <v>16.3</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="F82" s="3" t="n">
         <v>0.1</v>
@@ -3272,16 +3272,16 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>10.04</v>
+        <v>10.12</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F83" s="3" t="n">
         <v>0.04</v>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>13.51</v>
+        <v>13.27</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0.27</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>19.2</v>
+        <v>18.78</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>2.15</v>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>4.3</v>
+        <v>4.03</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>0</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>6.92</v>
+        <v>6.82</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.1</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1.04</v>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7.93</v>
+        <v>7.73</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6.55</v>
@@ -3724,28 +3724,28 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>16.53</v>
+        <v>15.97</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>13.47</v>
+        <v>13.3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>13.19</v>
+        <v>13.02</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>10.52</v>
+        <v>10.35</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10.52</v>
+        <v>10.35</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6.98</v>
+        <v>6.91</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6.49</v>
+        <v>6.42</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6.46</v>
+        <v>6.39</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>2.95</v>
@@ -3758,31 +3758,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>6.75</v>
+        <v>6.45</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6.35</v>
+        <v>6.18</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5.95</v>
+        <v>5.78</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5.54</v>
+        <v>5.38</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5.38</v>
+        <v>5.21</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4.13</v>
+        <v>3.97</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="8">
@@ -3792,28 +3792,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4.03</v>
+        <v>3.96</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.96</v>
+        <v>3.89</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -3863,28 +3863,28 @@
         <v>0.3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="G10" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>0.1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0</v>
@@ -3928,28 +3928,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0.1</v>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2.92</v>
+        <v>2.01</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>1.22</v>
@@ -3996,13 +3996,13 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>13.81</v>
+        <v>13.51</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>9.68</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>7.86</v>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>3.97</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>24.83</v>
+        <v>24.7</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>21.4</v>
+        <v>21.34</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>20.46</v>
+        <v>20.4</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>16.97</v>
+        <v>16.9</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>7.96</v>
+        <v>7.93</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>3.83</v>
@@ -4132,16 +4132,16 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>24.65</v>
+        <v>24.24</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>22.33</v>
+        <v>22.15</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>20.56</v>
+        <v>20.45</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>15.83</v>
+        <v>15.73</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>4.97</v>
@@ -4166,16 +4166,16 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>16.94</v>
+        <v>16.7</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>13.37</v>
+        <v>13.24</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>12.43</v>
+        <v>12.3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>11.02</v>
+        <v>10.85</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>4.03</v>
@@ -4200,28 +4200,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.03</v>
+        <v>4.79</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.28</v>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>1.21</v>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>13.12</v>
+        <v>12.4</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>8.58</v>
@@ -4379,22 +4379,22 @@
         <v>7.5</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="26">
@@ -4404,28 +4404,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>16.1</v>
+        <v>15.62</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>12.57</v>
+        <v>12.37</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>11.63</v>
+        <v>11.42</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>9.27</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>6.75</v>
+        <v>6.65</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>5.61</v>
+        <v>5.54</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>0.71</v>
@@ -4438,31 +4438,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.12</v>
+        <v>7.01</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>5.14</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H27" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I27" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="I27" s="3" t="n">
-        <v>1.42</v>
-      </c>
       <c r="J27" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="28">
@@ -4472,28 +4472,28 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>12.84</v>
+        <v>12.7</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>7.09</v>
+        <v>7.06</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>6.18</v>
+        <v>6.15</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.71</v>
@@ -4506,19 +4506,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>23.45</v>
+        <v>23.32</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>16.1</v>
+        <v>16.03</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>13.94</v>
+        <v>13.84</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>11.96</v>
+        <v>11.9</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>2.62</v>
@@ -4540,31 +4540,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>44.41</v>
+        <v>43.82</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>33.61</v>
+        <v>33.33</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>30.35</v>
+        <v>30.1</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>26.7</v>
+        <v>26.53</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>13.58</v>
+        <v>13.54</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>11.04</v>
+        <v>10.97</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>6.28</v>
+        <v>6.25</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="31">
@@ -4574,28 +4574,28 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>36.66</v>
+        <v>36.32</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>31.69</v>
+        <v>31.45</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>30.88</v>
+        <v>30.68</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>28.19</v>
+        <v>27.99</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>12.1</v>
+        <v>12.03</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.77</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>6.82</v>
+        <v>6.75</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>5.31</v>
+        <v>5.24</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>1.81</v>
@@ -4608,22 +4608,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>16.49</v>
+        <v>16.25</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>13.47</v>
+        <v>13.23</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>13.23</v>
+        <v>12.99</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>12.47</v>
+        <v>12.22</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>7.05</v>
+        <v>6.88</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>2.78</v>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>1.95</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1.75</v>
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>6.63</v>
+        <v>6.39</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>3.26</v>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>4.94</v>
+        <v>4.23</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>2.52</v>
@@ -4914,19 +4914,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>30.65</v>
+        <v>30.48</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>27.05</v>
+        <v>26.98</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>24.53</v>
+        <v>24.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>22.65</v>
+        <v>22.61</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>19.89</v>
+        <v>19.86</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>10.42</v>
@@ -4948,16 +4948,16 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>28.4</v>
+        <v>28.09</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>24.03</v>
+        <v>23.92</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>21.81</v>
+        <v>21.77</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>20.28</v>
+        <v>20.24</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>17.64</v>
@@ -4982,19 +4982,19 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>12.97</v>
+        <v>12.87</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>11.19</v>
+        <v>11.12</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>9.74</v>
+        <v>9.68</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>9.140000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>7.63</v>
+        <v>7.56</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>5.01</v>
@@ -5016,25 +5016,25 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>24.03</v>
+        <v>23.68</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>16.84</v>
+        <v>16.6</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>15</v>
+        <v>14.76</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>13.47</v>
+        <v>13.26</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>0.35</v>
@@ -5050,22 +5050,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>37.47</v>
+        <v>37.03</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>24.4</v>
+        <v>23.99</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>16.36</v>
+        <v>16.16</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>13.54</v>
+        <v>13.37</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>7.59</v>
+        <v>7.46</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>2.42</v>
@@ -5084,22 +5084,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>9.98</v>
+        <v>9.81</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>7.12</v>
+        <v>6.99</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>6.28</v>
+        <v>6.15</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>5.24</v>
+        <v>5.14</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.44</v>
@@ -5118,19 +5118,19 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>15.51</v>
+        <v>15.36</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>9.49</v>
+        <v>9.41</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>6.55</v>
+        <v>6.51</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0.82</v>
@@ -5152,19 +5152,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>15.39</v>
+        <v>15.22</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>11.39</v>
+        <v>11.36</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>10.62</v>
+        <v>10.58</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.58</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.06</v>
+        <v>7.02</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.9399999999999999</v>
@@ -5186,19 +5186,19 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>27.05</v>
+        <v>26.84</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>23.47</v>
+        <v>23.44</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>20.9</v>
+        <v>20.87</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>16.49</v>
+        <v>16.42</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>3.72</v>
@@ -5220,13 +5220,13 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>24.7</v>
+        <v>24.53</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>19.15</v>
+        <v>19.05</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>15.42</v>
+        <v>15.39</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>9.140000000000001</v>
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>18.4</v>
+        <v>18.19</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>15.03</v>
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>35.75</v>
+        <v>35.55</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>30.71</v>
@@ -5322,19 +5322,19 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>67.78</v>
+        <v>67.37</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>62.03</v>
+        <v>61.79</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>59.78</v>
+        <v>59.64</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>47.82</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>39.75</v>
+        <v>39.78</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>4.67</v>
@@ -5356,19 +5356,19 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>79.86</v>
+        <v>79.31</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>73.84999999999999</v>
+        <v>73.37</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>72.43000000000001</v>
+        <v>71.98</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46.7</v>
+        <v>46.49</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>46.25</v>
+        <v>46.04</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>10.69</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>81.45</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>75.84</v>
+        <v>75.13</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>71.81</v>
+        <v>71.17</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>47.08</v>
+        <v>46.67</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>7.63</v>
@@ -5411,7 +5411,7 @@
         <v>0.37</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="J55" s="3" t="n">
         <v>0</v>
@@ -5424,19 +5424,19 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>37.78</v>
+        <v>37.53</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>30.52</v>
+        <v>30.31</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>28.02</v>
+        <v>27.85</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>5.35</v>
+        <v>5.28</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0</v>
@@ -5458,16 +5458,16 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>34.38</v>
+        <v>34.07</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>27.45</v>
+        <v>27.18</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>24.73</v>
+        <v>24.46</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>12.87</v>
+        <v>12.77</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>9.27</v>
@@ -5492,19 +5492,19 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>8.4</v>
+        <v>8.27</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>5.38</v>
+        <v>5.24</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0</v>
@@ -5526,16 +5526,16 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>12.75</v>
+        <v>12.61</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>7.97</v>
+        <v>7.9</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>0.65</v>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>21.34</v>
+        <v>21.14</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>16.1</v>
+        <v>15.96</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>13.58</v>
+        <v>13.44</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>2.02</v>
@@ -5594,16 +5594,16 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>33.06</v>
+        <v>32.74</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>30.21</v>
+        <v>29.93</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>26.25</v>
+        <v>26.11</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>7.22</v>
@@ -5628,19 +5628,19 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>42.88</v>
+        <v>42.57</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>33.67</v>
+        <v>33.53</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>23.02</v>
+        <v>22.92</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>17.78</v>
+        <v>17.71</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>3.73</v>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>33.5</v>
+        <v>33.53</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>30.31</v>
+        <v>30.38</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>19.49</v>
@@ -5730,19 +5730,19 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>51.28</v>
+        <v>50.91</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>47.88</v>
+        <v>47.51</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>38.17</v>
+        <v>38.1</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>35.22</v>
+        <v>35.15</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>21.51</v>
+        <v>21.47</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>4.3</v>
@@ -5764,19 +5764,19 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>83.68000000000001</v>
+        <v>83.16</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>81.67</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>76.84</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>73.23</v>
+        <v>72.92</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>54.37</v>
+        <v>54.24</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>4.2</v>
@@ -5798,19 +5798,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>77.52</v>
+        <v>76.88</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>76.31</v>
+        <v>75.67</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>71.27</v>
+        <v>70.83</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>65.76000000000001</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>37.74</v>
+        <v>37.43</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>1.98</v>
@@ -5832,19 +5832,19 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>38.19</v>
+        <v>38.06</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>37.26</v>
+        <v>37.15</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>33.23</v>
+        <v>33.19</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>27.05</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.31</v>
@@ -5866,16 +5866,16 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>36.83</v>
+        <v>36.59</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>35.62</v>
+        <v>35.38</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>32.12</v>
+        <v>31.92</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>27.79</v>
+        <v>27.59</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>2.28</v>
@@ -5900,16 +5900,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>47.58</v>
+        <v>47.21</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>46.54</v>
+        <v>46.2</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>44.89</v>
+        <v>44.56</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>30.38</v>
+        <v>30.21</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0.1</v>
@@ -5934,16 +5934,16 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>47.02</v>
+        <v>46.43</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>46.06</v>
+        <v>45.68</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>43.3</v>
+        <v>43.01</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>15.77</v>
+        <v>15.74</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>1.15</v>
@@ -5968,16 +5968,16 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>35.75</v>
+        <v>35.28</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>33.9</v>
+        <v>33.6</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>31.05</v>
+        <v>30.75</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>0</v>
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>45.35</v>
+        <v>44.58</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>41.18</v>
+        <v>40.8</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>31.94</v>
+        <v>31.87</v>
       </c>
       <c r="E73" s="3" t="n">
         <v>2.99</v>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>25.2</v>
+        <v>24.87</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>22.65</v>
+        <v>22.58</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>9.880000000000001</v>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>33.96</v>
+        <v>33.72</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>31.46</v>
+        <v>31.39</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>14.24</v>
@@ -6104,10 +6104,10 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>43.85</v>
+        <v>43.75</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>11.53</v>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>70.5</v>
+        <v>70.13</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>67.23999999999999</v>
+        <v>66.97</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>26.81</v>
@@ -6172,16 +6172,16 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>88.65000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>84.51000000000001</v>
+        <v>83.89</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>33.54</v>
+        <v>33.51</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>17.92</v>
+        <v>17.88</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>3.78</v>
@@ -6206,16 +6206,16 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>77.89</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>70.26000000000001</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>23.45</v>
+        <v>23.32</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>15.29</v>
+        <v>15.26</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>1.92</v>
@@ -6240,13 +6240,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>71.84</v>
+        <v>71.08</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>55.52</v>
+        <v>55.07</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>4.06</v>
@@ -6274,13 +6274,13 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>59.58</v>
+        <v>57.73</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>25.74</v>
+        <v>25.4</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>6.35</v>
+        <v>6.28</v>
       </c>
       <c r="E81" s="3" t="n">
         <v>3.49</v>
@@ -6308,10 +6308,10 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>25.3</v>
+        <v>21.37</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>0.1</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>19.64</v>
+        <v>19.12</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>1.53</v>
@@ -6376,13 +6376,13 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>24.23</v>
+        <v>23.86</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>2.39</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E84" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>39.06</v>
+        <v>38.61</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>1.98</v>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>18.65</v>
+        <v>18.48</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>0.17</v>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>22.48</v>
+        <v>22.38</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>34.27</v>
+        <v>34.04</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0.84</v>
@@ -6658,7 +6658,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.03</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.1</v>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0.71</v>
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2.82</v>
+        <v>2.52</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1.34</v>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.28</v>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>2.02</v>
@@ -6896,31 +6896,31 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7.43</v>
+        <v>7.26</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -6930,16 +6930,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2.42</v>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0.54</v>
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.35</v>
+        <v>0.67</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.24</v>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5.83</v>
+        <v>4.79</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>2.6</v>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3.19</v>
+        <v>2.42</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1.01</v>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.17</v>
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.24</v>
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0.84</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>10.24</v>
+        <v>9.9</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>7.81</v>
@@ -7211,7 +7211,7 @@
         <v>7.15</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>6.18</v>
+        <v>6.15</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>3.37</v>
@@ -7236,19 +7236,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>10.15</v>
+        <v>9.68</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>7.06</v>
+        <v>6.96</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>6.45</v>
+        <v>6.38</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0.37</v>
@@ -7270,19 +7270,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>8.16</v>
+        <v>8.06</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.94</v>
+        <v>5.9</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5.28</v>
+        <v>5.24</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.28</v>
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>24.13</v>
+        <v>23.08</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>17.27</v>
+        <v>17.24</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>15.62</v>
@@ -7338,16 +7338,16 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>26.48</v>
+        <v>26.08</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>21.54</v>
+        <v>21.64</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>19.39</v>
+        <v>19.49</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.71</v>
+        <v>17.81</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>5.98</v>
@@ -7372,16 +7372,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>20.8</v>
+        <v>20.76</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>16.18</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>13.28</v>
+        <v>13.32</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>12.24</v>
+        <v>12.31</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>5.58</v>
@@ -7406,16 +7406,16 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>8.74</v>
+        <v>8.6</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5.81</v>
+        <v>5.75</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>0.64</v>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>16.08</v>
+        <v>15.73</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>11.46</v>
@@ -7452,7 +7452,7 @@
         <v>7.78</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.76</v>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>6.35</v>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>14.42</v>
+        <v>14.38</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>12.2</v>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>34.01</v>
+        <v>34.11</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>29.2</v>
+        <v>29.23</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>25.17</v>
@@ -7610,22 +7610,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>54.65</v>
+        <v>54.41</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>46.28</v>
+        <v>46.08</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>36.84</v>
+        <v>36.63</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>27.95</v>
+        <v>27.88</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5.1</v>
+        <v>5.07</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.87</v>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>69.42</v>
+        <v>69.59</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>59.24</v>
@@ -7653,7 +7653,7 @@
         <v>50.67</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>38.64</v>
+        <v>38.71</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>15.19</v>
@@ -7678,31 +7678,31 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>30.73</v>
+        <v>30.49</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>26.28</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>23.12</v>
+        <v>23.09</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>19.69</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33">
@@ -7712,22 +7712,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>43.99</v>
+        <v>43.78</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>36.12</v>
+        <v>35.92</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>30.51</v>
+        <v>30.44</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>24.63</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>10.75</v>
+        <v>10.72</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>5.44</v>
+        <v>5.48</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.24</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>22.11</v>
+        <v>21.98</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>17.88</v>
+        <v>17.67</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>13.98</v>
+        <v>13.88</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>11.26</v>
+        <v>11.19</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>1.34</v>
@@ -7780,19 +7780,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>29.99</v>
+        <v>29.84</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>25.37</v>
+        <v>25.3</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>19.79</v>
+        <v>19.57</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>17.41</v>
+        <v>17.34</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>9.19</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>1</v>
@@ -7814,19 +7814,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>34.21</v>
+        <v>34.04</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>28.63</v>
+        <v>28.6</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>20.77</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>17.34</v>
+        <v>17.37</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>2.89</v>
@@ -7848,16 +7848,16 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>15.83</v>
+        <v>15.76</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>14.2</v>
+        <v>14.17</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>12.22</v>
+        <v>12.19</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>10.9</v>
+        <v>10.87</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>7.29</v>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>5.71</v>
+        <v>5.75</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>5.24</v>
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>11.53</v>
+        <v>11.49</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>11.06</v>
@@ -7984,16 +7984,16 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>24.73</v>
+        <v>24.76</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>22.68</v>
+        <v>22.75</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>19.89</v>
+        <v>19.93</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>17.91</v>
+        <v>17.98</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>7.29</v>
@@ -8018,16 +8018,16 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>30.87</v>
+        <v>30.63</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>29.06</v>
+        <v>28.99</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>25.45</v>
+        <v>25.38</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>22.88</v>
+        <v>22.81</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>11.67</v>
@@ -8052,16 +8052,16 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>39.72</v>
+        <v>39.75</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>37.03</v>
+        <v>37.06</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>33.4</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>31.22</v>
+        <v>31.25</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>16.63</v>
@@ -8086,31 +8086,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>54.79</v>
+        <v>54.69</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>50.62</v>
+        <v>50.52</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>45.03</v>
+        <v>45</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>43.02</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>24.65</v>
+        <v>24.55</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>20.14</v>
+        <v>20</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>8.609999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="45">
@@ -8120,31 +8120,31 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>77.45</v>
+        <v>77.08</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>73.12</v>
+        <v>72.75</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>67.17</v>
+        <v>66.87</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>63.21</v>
+        <v>63.07</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>47.68</v>
+        <v>47.72</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>37</v>
+        <v>37.03</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>20.3</v>
+        <v>20.33</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="46">
@@ -8154,25 +8154,25 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>56.05</v>
+        <v>55.98</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>53.12</v>
+        <v>53.09</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>50.24</v>
+        <v>50.17</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>47.48</v>
+        <v>47.41</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>35.32</v>
+        <v>35.28</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>28.93</v>
+        <v>28.83</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>10.58</v>
+        <v>10.55</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>5.38</v>
@@ -8188,25 +8188,25 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>61.31</v>
+        <v>61.27</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>58.04</v>
+        <v>58</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>53.91</v>
+        <v>53.87</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>52.57</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>35.94</v>
+        <v>35.97</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>25.41</v>
+        <v>25.48</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>6.58</v>
+        <v>6.62</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>3.35</v>
@@ -8222,22 +8222,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>52.42</v>
+        <v>52.39</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>47.92</v>
+        <v>48.02</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>41.83</v>
+        <v>41.97</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>39.68</v>
+        <v>39.78</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>31.32</v>
+        <v>31.45</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>20.26</v>
+        <v>20.36</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>1.44</v>
@@ -8256,19 +8256,19 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>30.59</v>
+        <v>30.52</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>27.01</v>
+        <v>27.08</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>21.25</v>
+        <v>21.32</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>19.41</v>
+        <v>19.48</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>13.37</v>
+        <v>13.4</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>6.56</v>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>7.83</v>
+        <v>7.73</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>6.42</v>
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>23.3</v>
+        <v>23.19</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>20.17</v>
+        <v>20.14</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>16.46</v>
@@ -8358,19 +8358,19 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>32.76</v>
+        <v>32.33</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>27.96</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>22.61</v>
+        <v>22.28</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>19.39</v>
+        <v>19.46</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>15.59</v>
+        <v>15.62</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>11.66</v>
@@ -8392,22 +8392,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>28.12</v>
+        <v>28.19</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>22.98</v>
+        <v>22.78</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>20.19</v>
+        <v>20.26</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>16.63</v>
+        <v>16.7</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>10.79</v>
+        <v>10.82</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.1</v>
@@ -8426,13 +8426,13 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>67.08</v>
+        <v>67.19</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>62.85</v>
+        <v>62.88</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>60.52</v>
+        <v>60.49</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>59.06</v>
@@ -8441,7 +8441,7 @@
         <v>57.99</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>51.84</v>
+        <v>51.91</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>13.16</v>
@@ -8463,7 +8463,7 @@
         <v>64.68000000000001</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>60.42</v>
+        <v>60.55</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>53.06</v>
@@ -8475,16 +8475,16 @@
         <v>48.56</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>37.16</v>
+        <v>37.33</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>7.02</v>
+        <v>6.99</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>6.35</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="56">
@@ -8494,22 +8494,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>63.16</v>
+        <v>63.19</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>60.1</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>54.62</v>
+        <v>54.65</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>52.19</v>
+        <v>52.22</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>48.4</v>
+        <v>48.44</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>37.67</v>
+        <v>37.71</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>11.01</v>
@@ -8528,31 +8528,31 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>65.12</v>
+        <v>65.19</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>63.37</v>
+        <v>63.41</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>60.42</v>
+        <v>60.48</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>58.5</v>
+        <v>58.67</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>53.39</v>
+        <v>53.53</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>46.07</v>
+        <v>46.14</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>14.11</v>
+        <v>14.08</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>12.26</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>11.36</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="58">
@@ -8568,25 +8568,25 @@
         <v>57.63</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>48.49</v>
+        <v>48.52</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>42.57</v>
+        <v>42.64</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>38.61</v>
+        <v>38.71</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>32.36</v>
+        <v>32.49</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>17</v>
+        <v>17.04</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>11.86</v>
+        <v>11.9</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>11.29</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="59">
@@ -8596,25 +8596,25 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>61.93</v>
+        <v>61.89</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>61.17</v>
+        <v>61.21</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>55.5</v>
+        <v>55.53</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>52.08</v>
+        <v>52.16</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>50.47</v>
+        <v>50.57</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>38.4</v>
+        <v>38.51</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>16.24</v>
+        <v>16.2</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>7.61</v>
@@ -8630,22 +8630,22 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46.03</v>
+        <v>45.93</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>44.39</v>
+        <v>44.29</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>39.25</v>
+        <v>39.15</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>35.28</v>
+        <v>35.25</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>31.18</v>
+        <v>31.22</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>15.86</v>
+        <v>15.89</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>7.43</v>
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>28.75</v>
+        <v>28.72</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>26.25</v>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>12.4</v>
+        <v>12.43</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>9.74</v>
@@ -8800,19 +8800,19 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>41.8</v>
+        <v>41.87</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>38.78</v>
+        <v>38.81</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>35.28</v>
+        <v>35.35</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>33.17</v>
+        <v>33.2</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>21.07</v>
+        <v>21.1</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>10.05</v>
@@ -8834,22 +8834,22 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>73.16</v>
+        <v>73.12</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>64.65000000000001</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>61.6</v>
+        <v>61.74</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>57.81</v>
+        <v>57.85</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>44.69</v>
+        <v>44.83</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>21.67</v>
+        <v>21.7</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>8.720000000000001</v>
@@ -8868,25 +8868,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>87.87</v>
+        <v>87.77</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>85.22</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>82.69</v>
+        <v>82.83</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>80.91</v>
+        <v>81.08</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>63.84</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>39.45</v>
+        <v>39.52</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>23.62</v>
+        <v>23.66</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>8.6</v>
@@ -8908,25 +8908,25 @@
         <v>58.33</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>54.65</v>
+        <v>54.69</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46.7</v>
+        <v>46.74</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>29.1</v>
+        <v>29.13</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>22.05</v>
+        <v>22.08</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>16.49</v>
+        <v>16.53</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>5.94</v>
+        <v>6.01</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="69">
@@ -8936,25 +8936,25 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>70.45999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>68.72</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>64.45</v>
+        <v>64.38</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>54.77</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>32.33</v>
+        <v>32.26</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>24.7</v>
+        <v>24.63</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>19.22</v>
+        <v>19.19</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>6.72</v>
@@ -8970,25 +8970,25 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>62.33</v>
+        <v>62.13</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>61.36</v>
+        <v>61.19</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>56.45</v>
+        <v>56.25</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>50.57</v>
+        <v>50.44</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>28.33</v>
+        <v>28.46</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>20.43</v>
+        <v>20.5</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>13.24</v>
+        <v>13.27</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>4.81</v>
@@ -9004,22 +9004,22 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>53.35</v>
+        <v>53.2</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>51.53</v>
+        <v>51.49</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>46.76</v>
+        <v>46.73</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>36.24</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>15.89</v>
+        <v>15.92</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>4.72</v>
@@ -9038,25 +9038,25 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>40.83</v>
+        <v>40.66</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>35.42</v>
+        <v>35.45</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>28.46</v>
+        <v>28.53</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>11.42</v>
+        <v>11.46</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>5.51</v>
+        <v>5.58</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0.44</v>
@@ -9072,13 +9072,13 @@
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>40.83</v>
+        <v>40.62</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>36.08</v>
+        <v>36.11</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>30.45</v>
+        <v>30.52</v>
       </c>
       <c r="E73" s="3" t="n">
         <v>8.92</v>
@@ -9106,13 +9106,13 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>30.51</v>
+        <v>30.41</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>28.56</v>
+        <v>28.76</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>18.68</v>
+        <v>18.62</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>5.51</v>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>5.24</v>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>24.06</v>
+        <v>23.92</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>14.72</v>
+        <v>14.75</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>0.67</v>
@@ -9242,16 +9242,16 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>66.67</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>45.83</v>
+        <v>46.01</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>17.88</v>
+        <v>17.95</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>8.44</v>
+        <v>8.51</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>6.7</v>
@@ -9276,25 +9276,25 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>70.36</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>57.66</v>
+        <v>57.83</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>27.08</v>
+        <v>27.15</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>15.32</v>
+        <v>15.36</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>8.74</v>
+        <v>8.77</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>7.39</v>
+        <v>7.43</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>0.3</v>
@@ -9310,13 +9310,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>88.3</v>
+        <v>88.06</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>28.85</v>
+        <v>28.92</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>16.81</v>
@@ -9344,31 +9344,31 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>71.27</v>
+        <v>70.97</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>50.67</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>34.78</v>
+        <v>34.81</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>25.24</v>
+        <v>25.37</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>23.79</v>
+        <v>23.92</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>13.41</v>
+        <v>13.51</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>7.93</v>
+        <v>7.96</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>7.46</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="82">
@@ -9378,25 +9378,25 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>53.97</v>
+        <v>53.8</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>28.53</v>
+        <v>28.43</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>16.4</v>
+        <v>16.47</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>12.03</v>
+        <v>12.1</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>9.91</v>
+        <v>9.98</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>6.15</v>
+        <v>6.22</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>2.99</v>
@@ -9412,16 +9412,16 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>48.14</v>
+        <v>48.1</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>15.1</v>
+        <v>15.14</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>7.92</v>
+        <v>7.96</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="F83" s="3" t="n">
         <v>2.01</v>
@@ -9446,25 +9446,25 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>54.13</v>
+        <v>54.2</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>12.77</v>
+        <v>12.84</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>10.35</v>
+        <v>10.42</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>4.94</v>
+        <v>4.97</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>0.03</v>
@@ -9480,19 +9480,19 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>56.49</v>
+        <v>56.35</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>21.25</v>
+        <v>21.35</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>10.24</v>
+        <v>10.31</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>7.81</v>
+        <v>7.85</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>5.97</v>
+        <v>6.01</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>4.62</v>
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>21.64</v>
+        <v>21.4</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>0.03</v>
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>14.35</v>
+        <v>14.11</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>1.24</v>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>22.55</v>
+        <v>22.51</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>3.26</v>
@@ -9762,7 +9762,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1.08</v>
@@ -9796,7 +9796,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5.58</v>
+        <v>5.48</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3.9</v>
@@ -9830,31 +9830,31 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>14.08</v>
+        <v>13.84</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>11.39</v>
+        <v>11.36</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>11.36</v>
+        <v>11.32</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>11.26</v>
+        <v>11.22</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>9.34</v>
+        <v>9.31</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6.35</v>
+        <v>6.32</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>5.88</v>
+        <v>5.85</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="6">
@@ -9864,31 +9864,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>15</v>
+        <v>14.69</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12.64</v>
+        <v>12.5</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12.57</v>
+        <v>12.43</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>12.36</v>
+        <v>12.22</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>11.01</v>
+        <v>10.87</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>6.94</v>
+        <v>6.88</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6.84</v>
+        <v>6.77</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="7">
@@ -9898,31 +9898,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>11.49</v>
+        <v>11.46</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>10.99</v>
+        <v>10.95</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>10.82</v>
+        <v>10.79</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>10.11</v>
+        <v>10.08</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>9.34</v>
+        <v>9.24</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>8.84</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="8">
@@ -9932,22 +9932,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>14.69</v>
+        <v>14.76</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12.47</v>
+        <v>12.57</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>12.26</v>
+        <v>12.36</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>11.81</v>
+        <v>11.91</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>11.42</v>
+        <v>11.53</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>8.609999999999999</v>
@@ -9966,22 +9966,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>5.28</v>
+        <v>5.07</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.8100000000000001</v>
@@ -10000,16 +10000,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6.59</v>
+        <v>6.62</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>1.61</v>
@@ -10034,31 +10034,31 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>13.47</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>12.9</v>
+        <v>12.97</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>12.86</v>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>12.79</v>
-      </c>
       <c r="F11" s="3" t="n">
-        <v>7.11</v>
+        <v>7.15</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>6.36</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>6.32</v>
-      </c>
       <c r="I11" s="3" t="n">
-        <v>6.11</v>
+        <v>6.14</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="12">
@@ -10068,7 +10068,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5.24</v>
+        <v>3.7</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>2.65</v>
@@ -10102,7 +10102,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>7.5</v>
+        <v>6.74</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>3.4</v>
@@ -10136,7 +10136,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5.68</v>
+        <v>5.01</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1.98</v>
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.9</v>
@@ -10204,31 +10204,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.96</v>
+        <v>2.55</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I16" s="3" t="n">
         <v>0.54</v>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="J16" s="3" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17">
@@ -10272,31 +10272,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>32.15</v>
+        <v>32.12</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>27.12</v>
+        <v>27.26</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>26.81</v>
+        <v>26.94</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>25.49</v>
+        <v>25.62</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>12.99</v>
+        <v>13.09</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11.7</v>
+        <v>11.81</v>
       </c>
       <c r="H18" s="3" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>10.28</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>10.24</v>
-      </c>
       <c r="J18" s="3" t="n">
-        <v>9.58</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -10306,31 +10306,31 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>22.65</v>
+        <v>22.24</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>19.05</v>
+        <v>18.95</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>18.21</v>
+        <v>18.11</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>17.67</v>
+        <v>17.64</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>10.72</v>
+        <v>10.75</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>8.57</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>8.529999999999999</v>
-      </c>
       <c r="J19" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="20">
@@ -10340,28 +10340,28 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>19.38</v>
+        <v>19.24</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>15.94</v>
+        <v>15.9</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>15.56</v>
+        <v>15.52</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>15.24</v>
+        <v>15.21</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>8.539999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>7.22</v>
+        <v>7.19</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>4.65</v>
@@ -10374,31 +10374,31 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>33.97</v>
+        <v>33.43</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>28.12</v>
+        <v>28.26</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>27.02</v>
+        <v>27.15</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>26.11</v>
+        <v>26.24</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>16.16</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12.97</v>
+        <v>13</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.72</v>
+        <v>10.75</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>10.55</v>
+        <v>10.58</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="22">
@@ -10408,22 +10408,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>32.69</v>
+        <v>32.49</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>27.18</v>
+        <v>27.32</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>25.03</v>
+        <v>25.17</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>22.08</v>
+        <v>22.21</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>11.63</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>8.029999999999999</v>
@@ -10442,19 +10442,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>33.97</v>
+        <v>34.23</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>29.72</v>
+        <v>30.02</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>28.05</v>
+        <v>28.35</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>27.08</v>
+        <v>27.42</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>14.77</v>
+        <v>14.73</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>11.31</v>
@@ -10476,31 +10476,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>21.1</v>
+        <v>21.07</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>18.78</v>
+        <v>18.82</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>17.88</v>
+        <v>17.91</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>16.47</v>
+        <v>16.5</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>9.51</v>
+        <v>9.58</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>8.84</v>
+        <v>8.9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>17.6</v>
+        <v>17.26</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>12.5</v>
@@ -10522,10 +10522,10 @@
         <v>8.09</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4.55</v>
+        <v>4.51</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>2.22</v>
@@ -10544,7 +10544,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>8.699999999999999</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>15.36</v>
+        <v>15.29</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>12.67</v>
@@ -10627,7 +10627,7 @@
         <v>4.4</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>2.62</v>
@@ -10646,16 +10646,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>38.81</v>
+        <v>38.94</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>33</v>
+        <v>33.06</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>29.67</v>
+        <v>29.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>22.65</v>
+        <v>22.68</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>9.140000000000001</v>
@@ -10680,22 +10680,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>62.74</v>
+        <v>62.64</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>56.6</v>
+        <v>56.53</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>50.69</v>
+        <v>50.66</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>42.15</v>
+        <v>42.12</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>16.35</v>
+        <v>16.32</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>14.41</v>
+        <v>14.37</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>12.29</v>
@@ -10714,31 +10714,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>80.84999999999999</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>74.45999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>70.06</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>64.48</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46.37</v>
+        <v>46.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>26.78</v>
+        <v>26.71</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.82</v>
+        <v>18.75</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>17.88</v>
+        <v>17.81</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>15.29</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="32">
@@ -10748,31 +10748,31 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>42.01</v>
+        <v>41.88</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>38.51</v>
+        <v>38.58</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>36.6</v>
+        <v>36.63</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>34.51</v>
+        <v>34.62</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>22.92</v>
+        <v>22.95</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>12.81</v>
+        <v>12.74</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>9.1</v>
+        <v>8.99</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="33">
@@ -10782,31 +10782,31 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>50.5</v>
+        <v>50.37</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>42.14</v>
+        <v>42</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>38.98</v>
+        <v>39.01</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>34.17</v>
+        <v>34.24</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>24.29</v>
+        <v>24.5</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>4.87</v>
+        <v>4.84</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -10822,22 +10822,22 @@
         <v>28.8</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>26.61</v>
+        <v>26.75</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>25.34</v>
+        <v>25.44</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>16.53</v>
+        <v>16.63</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>5.51</v>
+        <v>5.54</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>2.12</v>
@@ -10850,28 +10850,28 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>41.44</v>
+        <v>41.37</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>37.87</v>
+        <v>37.91</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>34.75</v>
+        <v>34.78</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>32.4</v>
+        <v>32.44</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>21.54</v>
+        <v>21.65</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>5.95</v>
+        <v>6.03</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4.87</v>
+        <v>4.95</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>3.2</v>
@@ -10884,31 +10884,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>36.59</v>
+        <v>36.49</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>31.89</v>
+        <v>31.92</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>26.58</v>
+        <v>26.61</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>23.62</v>
+        <v>23.72</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>18.82</v>
+        <v>18.92</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.06</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="37">
@@ -10921,28 +10921,28 @@
         <v>25.03</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>23.09</v>
+        <v>23.12</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>22.01</v>
+        <v>22.05</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>20.97</v>
+        <v>21.01</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>17.78</v>
+        <v>17.85</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>8.06</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
       <c r="I37" s="3" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J37" s="3" t="n">
         <v>6.49</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>6.46</v>
       </c>
     </row>
     <row r="38">
@@ -10952,16 +10952,16 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>21.81</v>
+        <v>21.88</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>21.47</v>
+        <v>21.54</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>21.14</v>
+        <v>21.2</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>20.9</v>
+        <v>20.97</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>16.97</v>
@@ -10986,31 +10986,31 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>14.44</v>
+        <v>14.55</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>14.03</v>
+        <v>14.13</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>13.51</v>
+        <v>13.61</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.23</v>
+        <v>13.33</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>10.1</v>
+        <v>10.17</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="40">
@@ -11020,22 +11020,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>22.98</v>
+        <v>22.92</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>22.72</v>
+        <v>22.68</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>21.34</v>
+        <v>21.3</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>21.07</v>
+        <v>21.03</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>15.52</v>
+        <v>15.46</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10.65</v>
+        <v>10.58</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>5.44</v>
@@ -11054,22 +11054,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>34.31</v>
+        <v>34.48</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>32.83</v>
+        <v>33.03</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>31.12</v>
+        <v>31.28</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>29.4</v>
+        <v>29.64</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>22.88</v>
+        <v>23.08</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>13.58</v>
+        <v>13.68</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>8.94</v>
@@ -11088,31 +11088,31 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>45.03</v>
+        <v>45</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>43.47</v>
+        <v>43.54</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>40.59</v>
+        <v>40.66</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>38.06</v>
+        <v>38.16</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>28.92</v>
+        <v>28.99</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>23.12</v>
+        <v>23.19</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>15.94</v>
+        <v>15.97</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>13.51</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>6.77</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="43">
@@ -11122,28 +11122,28 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>52.86</v>
+        <v>52.96</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>50.94</v>
+        <v>51.04</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>48.69</v>
+        <v>48.79</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46.03</v>
+        <v>46.14</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>38.58</v>
+        <v>38.64</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>33.43</v>
+        <v>33.53</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>28.43</v>
+        <v>28.53</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>18.75</v>
+        <v>18.78</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>12.06</v>
@@ -11156,31 +11156,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>61.88</v>
+        <v>61.84</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>58.02</v>
+        <v>58.06</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>56.15</v>
+        <v>56.22</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>53.61</v>
+        <v>53.72</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>43.61</v>
+        <v>43.68</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>39.65</v>
+        <v>39.72</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>34.13</v>
+        <v>34.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>18.33</v>
+        <v>18.26</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.21</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="45">
@@ -11190,31 +11190,31 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>82.53</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>79.06999999999999</v>
+        <v>78.83</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>75.47</v>
+        <v>75.27</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>72.01000000000001</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>63.78</v>
+        <v>63.81</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>55.31</v>
+        <v>55.54</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>38.98</v>
+        <v>39.15</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>20.43</v>
+        <v>20.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>9.74</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -11224,31 +11224,31 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>58.64</v>
+        <v>58.7</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>56.45</v>
+        <v>56.55</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>54.57</v>
+        <v>54.64</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>52.92</v>
+        <v>52.99</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>45.67</v>
+        <v>45.7</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>36.42</v>
+        <v>36.49</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>11.59</v>
+        <v>11.63</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.96</v>
+        <v>6.99</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.81</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="47">
@@ -11258,31 +11258,31 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>63.73</v>
+        <v>63.84</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>60.31</v>
+        <v>60.38</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>57.37</v>
+        <v>57.44</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>55.62</v>
+        <v>55.73</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>40.77</v>
+        <v>41.07</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>24.44</v>
+        <v>24.59</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>7.7</v>
+        <v>7.74</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>6.73</v>
+        <v>6.77</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>6.25</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="48">
@@ -11295,16 +11295,16 @@
         <v>57.22</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>53.36</v>
+        <v>53.46</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>48.86</v>
+        <v>49.03</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46.47</v>
+        <v>46.67</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>38.17</v>
+        <v>38.37</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>17.71</v>
@@ -11329,28 +11329,28 @@
         <v>42.05</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>39.62</v>
+        <v>39.72</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>36.74</v>
+        <v>36.84</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>34.17</v>
+        <v>34.31</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>29.13</v>
+        <v>29.2</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>13.33</v>
+        <v>13.37</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>8.51</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>8.02</v>
+        <v>8.06</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>7.92</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="50">
@@ -11363,19 +11363,19 @@
         <v>15.42</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>14.65</v>
+        <v>14.72</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>13.68</v>
+        <v>13.74</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>12.57</v>
+        <v>12.63</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>11.32</v>
+        <v>11.39</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>6.28</v>
+        <v>6.35</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>2.59</v>
@@ -11397,16 +11397,16 @@
         <v>29.69</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>27.85</v>
+        <v>27.88</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>25.83</v>
+        <v>25.9</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>24.41</v>
+        <v>24.44</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>22.19</v>
+        <v>22.22</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>15.03</v>
@@ -11428,22 +11428,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>35.69</v>
+        <v>35.38</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>31.65</v>
+        <v>31.72</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>27.59</v>
+        <v>27.69</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>24.87</v>
+        <v>24.93</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>21.07</v>
+        <v>21.14</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>14.62</v>
+        <v>14.65</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>5.88</v>
@@ -11462,22 +11462,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>39.92</v>
+        <v>39.89</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>35.82</v>
+        <v>35.95</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>33.47</v>
+        <v>33.6</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>31.55</v>
+        <v>31.69</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>29</v>
+        <v>29.13</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>20.46</v>
+        <v>20.5</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>9.880000000000001</v>
@@ -11496,22 +11496,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>69.83</v>
+        <v>70</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>64.06</v>
+        <v>64.17</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>62.64</v>
+        <v>62.78</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>60.8</v>
+        <v>60.94</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>45.73</v>
+        <v>45.62</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>16.53</v>
@@ -11520,7 +11520,7 @@
         <v>11.18</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>10.35</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="55">
@@ -11530,25 +11530,25 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>72.38</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>70.03</v>
+        <v>70.16</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>64.34999999999999</v>
+        <v>64.45</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>62.57</v>
+        <v>62.63</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>60.01</v>
+        <v>60.11</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>17.24</v>
+        <v>17.27</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>13.24</v>
@@ -11564,31 +11564,31 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>68.58</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>66.53</v>
+        <v>66.63</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62.6</v>
+        <v>62.74</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>60.62</v>
+        <v>60.8</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>56.28</v>
+        <v>56.39</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>33.26</v>
+        <v>33.33</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>14.93</v>
+        <v>14.97</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>13.09</v>
+        <v>13.12</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>11.42</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="57">
@@ -11598,31 +11598,31 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>67.73999999999999</v>
+        <v>67.88</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>66.3</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>64.38</v>
+        <v>64.55</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>61.73</v>
+        <v>61.96</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>56.96</v>
+        <v>57.19</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>37.9</v>
+        <v>38.04</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>19.89</v>
+        <v>20.03</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>17</v>
+        <v>17.14</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>14.31</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="58">
@@ -11632,31 +11632,31 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>64.55</v>
+        <v>64.72</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>63.04</v>
+        <v>63.21</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>57.76</v>
+        <v>57.93</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>49.73</v>
+        <v>49.93</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>45.13</v>
+        <v>45.3</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>29.84</v>
+        <v>29.91</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>16.63</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>14.21</v>
+        <v>14.25</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>12.77</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="59">
@@ -11666,31 +11666,31 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>72.88</v>
+        <v>72.84</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>71.98</v>
+        <v>72.02</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>66.84999999999999</v>
+        <v>66.95</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>63.15</v>
+        <v>63.29</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>59.27</v>
+        <v>59.45</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>31.07</v>
+        <v>31.18</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>14.04</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>9.59</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>8.84</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -11706,13 +11706,13 @@
         <v>46.94</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>42.2</v>
+        <v>42.17</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>38.61</v>
+        <v>38.64</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>31.92</v>
+        <v>31.99</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>12.63</v>
@@ -11737,16 +11737,16 @@
         <v>34.13</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>31.87</v>
+        <v>31.91</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>24.93</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>21.28</v>
+        <v>21.32</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>17.36</v>
+        <v>17.4</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>4.13</v>
@@ -11768,19 +11768,19 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>19.22</v>
+        <v>19.35</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>18.35</v>
+        <v>18.48</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>15.83</v>
+        <v>15.89</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>14.11</v>
+        <v>14.21</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>11.93</v>
+        <v>12.03</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>2.28</v>
@@ -11802,16 +11802,16 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>10.87</v>
+        <v>10.9</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>9.550000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>5.73</v>
+        <v>5.76</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>4.97</v>
@@ -11836,28 +11836,28 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>27.45</v>
+        <v>27.69</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>26.98</v>
+        <v>27.18</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>26.04</v>
+        <v>26.24</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>24.33</v>
+        <v>24.53</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>22.21</v>
+        <v>22.41</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>6.15</v>
+        <v>6.18</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>5.01</v>
@@ -11870,31 +11870,31 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>55.38</v>
+        <v>55.58</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>53.56</v>
+        <v>53.76</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>52.02</v>
+        <v>52.25</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>48.99</v>
+        <v>49.23</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>42.54</v>
+        <v>42.74</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>12.4</v>
+        <v>12.43</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>6.08</v>
+        <v>6.12</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="66">
@@ -11904,31 +11904,31 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>80.8</v>
+        <v>80.87</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>74.62</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>72.47</v>
+        <v>72.64</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>68.58</v>
+        <v>68.78</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>56.22</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>19.34</v>
+        <v>19.41</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>6.32</v>
+        <v>6.39</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>5.8</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="67">
@@ -11938,22 +11938,22 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>92.84</v>
+        <v>92.81</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.87</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>90.73</v>
+        <v>90.86</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>87.67</v>
+        <v>87.77</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>75.91</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>36.86</v>
+        <v>36.96</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>22.55</v>
@@ -11972,31 +11972,31 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>65</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>64.03</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>61.7</v>
+        <v>61.94</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>53.33</v>
+        <v>53.54</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>34.27</v>
+        <v>34.31</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>23.54</v>
+        <v>23.58</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>15.94</v>
+        <v>16.01</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>10.66</v>
+        <v>10.73</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>10.03</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="69">
@@ -12006,31 +12006,31 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>75.91</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>74.45999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>70.73</v>
+        <v>70.77</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>60.58</v>
+        <v>60.62</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>33.57</v>
+        <v>33.4</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>25.47</v>
+        <v>25.37</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>15.89</v>
+        <v>15.73</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>9.44</v>
+        <v>9.41</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="70">
@@ -12040,31 +12040,31 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.53</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>70.16</v>
+        <v>70.09</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>64.84999999999999</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>57.02</v>
+        <v>57.16</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>31.92</v>
+        <v>32.09</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>23.69</v>
+        <v>23.82</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>19.49</v>
+        <v>19.59</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>14.92</v>
+        <v>15.02</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>13.51</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="71">
@@ -12074,19 +12074,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>71.84</v>
+        <v>71.95</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>70.8</v>
+        <v>70.91</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>67.89</v>
+        <v>67.97</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>53.94</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>28.35</v>
+        <v>28.39</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>21.73</v>
@@ -12098,7 +12098,7 @@
         <v>16.96</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>15.74</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="72">
@@ -12111,28 +12111,28 @@
         <v>56.72</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>51.85</v>
+        <v>52.02</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>47.95</v>
+        <v>48.08</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>26.41</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>15.15</v>
+        <v>15.12</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>11.9</v>
+        <v>11.86</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>11.29</v>
+        <v>11.26</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>10.79</v>
+        <v>10.75</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>9.07</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -12145,28 +12145,28 @@
         <v>43.3</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>38.54</v>
+        <v>38.65</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>31.81</v>
+        <v>31.94</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>6.91</v>
+        <v>6.94</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="74">
@@ -12176,31 +12176,31 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>32.9</v>
+        <v>32.93</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>31.05</v>
+        <v>31.25</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>21.61</v>
+        <v>21.71</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>6.85</v>
+        <v>6.92</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>4.91</v>
+        <v>4.97</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="I74" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J74" s="3" t="n">
         <v>3.26</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>3.19</v>
       </c>
     </row>
     <row r="75">
@@ -12210,19 +12210,19 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>21.39</v>
+        <v>21.46</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>19.27</v>
+        <v>19.34</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>12.36</v>
+        <v>12.47</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>5.24</v>
+        <v>5.31</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>3.37</v>
@@ -12244,13 +12244,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>35.92</v>
+        <v>36.12</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>33.3</v>
+        <v>33.53</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>14.92</v>
+        <v>13.47</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>4.97</v>
@@ -12278,22 +12278,22 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>42.71</v>
+        <v>42.78</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>35.45</v>
+        <v>35.62</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>9.58</v>
+        <v>8.94</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>2.92</v>
@@ -12312,22 +12312,22 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>73.58</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>58.89</v>
+        <v>59.13</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>17.57</v>
+        <v>17.53</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>10.03</v>
+        <v>10.1</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>8.23</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>3.96</v>
@@ -12346,31 +12346,31 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>78.83</v>
+        <v>79.03</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>32.83</v>
+        <v>32.86</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>21.71</v>
+        <v>21.84</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>14.92</v>
+        <v>15.05</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>10.05</v>
+        <v>10.18</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>8.06</v>
+        <v>8.17</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="80">
@@ -12380,31 +12380,31 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>92.36</v>
+        <v>92.33</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>76.45999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>27.5</v>
+        <v>27.57</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>18.54</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>14.41</v>
+        <v>14.44</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>9.789999999999999</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>6.11</v>
+        <v>6.18</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="81">
@@ -12414,31 +12414,31 @@
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>88.64</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>65.86</v>
+        <v>65.89</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>41.53</v>
+        <v>41.6</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>36.79</v>
+        <v>36.9</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>34.71</v>
+        <v>34.85</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>31.32</v>
+        <v>31.45</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>23.62</v>
+        <v>23.72</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>21.34</v>
+        <v>21.4</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>20.16</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="82">
@@ -12448,31 +12448,31 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>69.93000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>40.49</v>
+        <v>40.56</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>24.03</v>
+        <v>24.26</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>22.01</v>
+        <v>22.21</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>20.46</v>
+        <v>20.56</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>18.25</v>
+        <v>18.35</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>10.32</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>8.27</v>
+        <v>8.23</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>7.22</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="83">
@@ -12482,31 +12482,31 @@
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>67.67</v>
+        <v>67.63</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>32.03</v>
+        <v>32.07</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>14.99</v>
+        <v>15.14</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>14.14</v>
+        <v>14.25</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>13.13</v>
+        <v>13.24</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>10.45</v>
+        <v>10.57</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>8.85</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>8.59</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="84">
@@ -12516,31 +12516,31 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>61.09</v>
+        <v>61.29</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>36.12</v>
+        <v>36.39</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>22.14</v>
+        <v>22.28</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>20.7</v>
+        <v>20.83</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>19.15</v>
+        <v>19.29</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>16.97</v>
+        <v>17.1</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>12.47</v>
+        <v>12.6</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>11.53</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="85">
@@ -12550,13 +12550,13 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>54.17</v>
+        <v>54.13</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>18.23</v>
+        <v>18.3</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>6.98</v>
+        <v>7.01</v>
       </c>
       <c r="E85" s="3" t="n">
         <v>6.18</v>
@@ -12584,10 +12584,10 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>18.51</v>
+        <v>18.31</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -12618,7 +12618,7 @@
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>21.53</v>
+        <v>21.56</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>0.9</v>
@@ -12652,19 +12652,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>22.28</v>
+        <v>22.18</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>6.65</v>
+        <v>6.72</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>1.61</v>
@@ -12686,10 +12686,10 @@
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>29.23</v>
+        <v>29.33</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>4.77</v>
+        <v>4.81</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>1.88</v>
@@ -12798,7 +12798,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -13036,25 +13036,25 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0.03</v>
@@ -13070,31 +13070,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -13138,7 +13138,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.6</v>
@@ -13206,25 +13206,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>6.75</v>
+        <v>6.38</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0</v>
@@ -13274,7 +13274,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0.2</v>
@@ -13376,16 +13376,16 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>8.17</v>
+        <v>8.06</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>2.35</v>
@@ -13444,16 +13444,16 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7.49</v>
+        <v>7.33</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>5.01</v>
+        <v>5.04</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>4.91</v>
+        <v>4.94</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>4.54</v>
+        <v>4.57</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>2.62</v>
@@ -13580,7 +13580,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>6.01</v>
+        <v>5.94</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>0.9</v>
@@ -13614,7 +13614,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>0.3</v>
@@ -13648,16 +13648,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.17</v>
@@ -13682,16 +13682,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>12.4</v>
+        <v>12.47</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>6.99</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0.4</v>
@@ -13716,13 +13716,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>29.81</v>
+        <v>29.94</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>15.56</v>
+        <v>15.62</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.26</v>
+        <v>11.29</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>3.43</v>
@@ -13750,16 +13750,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>45.38</v>
+        <v>45.35</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>21.39</v>
+        <v>21.28</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>12.74</v>
+        <v>12.67</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>6.25</v>
+        <v>6.18</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>0.38</v>
@@ -13784,13 +13784,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>55.81</v>
+        <v>55.95</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>25.74</v>
+        <v>25.81</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>19.15</v>
+        <v>19.25</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>7.06</v>
@@ -13818,7 +13818,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>13.78</v>
+        <v>13.68</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>4.97</v>
@@ -13827,7 +13827,7 @@
         <v>3.89</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>1.15</v>
@@ -13858,7 +13858,7 @@
         <v>4.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>0.37</v>
@@ -13886,16 +13886,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3.76</v>
+        <v>3.83</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.37</v>
@@ -13932,7 +13932,7 @@
         <v>2.64</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -13954,7 +13954,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>2.86</v>
@@ -14226,13 +14226,13 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>7.57</v>
+        <v>7.47</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>4.97</v>
@@ -14365,13 +14365,13 @@
         <v>6.85</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.07</v>
+        <v>5.04</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>4.47</v>
@@ -14430,10 +14430,10 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>0.34</v>
@@ -14464,7 +14464,7 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>13.89</v>
+        <v>13.85</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>7.88</v>
@@ -14498,16 +14498,16 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>30.48</v>
+        <v>30.38</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>20.83</v>
+        <v>20.87</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>9.710000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>8.17</v>
+        <v>8.23</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>1.01</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>19.46</v>
+        <v>19.56</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>9.949999999999999</v>
@@ -14566,19 +14566,19 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>21.67</v>
+        <v>21.77</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>12.67</v>
+        <v>12.64</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>11.74</v>
+        <v>11.7</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>11.15</v>
+        <v>11.11</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>9.41</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.31</v>
@@ -14600,19 +14600,19 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>8.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0.2</v>
@@ -14668,19 +14668,19 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>8</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>7.66</v>
+        <v>7.69</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>6.96</v>
+        <v>6.99</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>6.72</v>
+        <v>6.75</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>5.31</v>
+        <v>5.34</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0.07000000000000001</v>
@@ -14736,19 +14736,19 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>9.34</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>8.48</v>
+        <v>8.51</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>7.94</v>
+        <v>7.97</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>7.51</v>
+        <v>7.54</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>5.85</v>
+        <v>5.89</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>0.5</v>
@@ -14770,19 +14770,19 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0</v>
@@ -14940,7 +14940,7 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>4.84</v>
+        <v>4.87</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>3.23</v>
@@ -14974,19 +14974,19 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>50.31</v>
+        <v>50.28</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>6.91</v>
+        <v>6.84</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>6.22</v>
+        <v>6.18</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>5.28</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0.03</v>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>18.55</v>
+        <v>18.45</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>2.28</v>
@@ -15042,19 +15042,19 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>8.58</v>
+        <v>8.65</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>8.06</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>6.63</v>
+        <v>6.67</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.31</v>
@@ -15076,16 +15076,16 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>24.66</v>
+        <v>24.6</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>23.42</v>
+        <v>23.35</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>22.14</v>
+        <v>22.08</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>16.13</v>
+        <v>16.1</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>1.41</v>
@@ -15110,22 +15110,22 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>7.8</v>
+        <v>7.76</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>7.39</v>
+        <v>7.36</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>7.16</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>5.75</v>
+        <v>5.81</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>4.3</v>
+        <v>4.37</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0</v>
@@ -15144,19 +15144,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0.93</v>
@@ -15382,7 +15382,7 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>20.66</v>
+        <v>20.62</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0.97</v>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>19.46</v>
+        <v>19.42</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>1.61</v>
@@ -15450,7 +15450,7 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>5.76</v>
+        <v>5.73</v>
       </c>
       <c r="C80" s="3" t="n">
         <v>1.74</v>
@@ -15722,7 +15722,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>6.59</v>
+        <v>6.52</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.27</v>

--- a/outputs/All_States_negative_prices.xlsx
+++ b/outputs/All_States_negative_prices.xlsx
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -76,7 +78,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
